--- a/hyperparameter_tuning_results.xlsx
+++ b/hyperparameter_tuning_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruno\OneDrive\Escritorio\Desktop\Repositories\Programming_math_Ai_Assessmment_Msc_Ai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAFC22BE-9EE3-4EA0-A97F-BD7DD659223D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5133380D-9235-4EA3-8A06-8B49D3168133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="30">
   <si>
     <t>Description</t>
   </si>
@@ -28,55 +28,49 @@
     <t>Architecture</t>
   </si>
   <si>
-    <t>epoch</t>
-  </si>
-  <si>
-    <t>learning_rate</t>
-  </si>
-  <si>
     <t>seed</t>
   </si>
   <si>
-    <t>hidden_activation</t>
-  </si>
-  <si>
-    <t>output_activation</t>
-  </si>
-  <si>
-    <t>dropout_rate</t>
-  </si>
-  <si>
-    <t>lambda_l1</t>
-  </si>
-  <si>
-    <t>lambda_l2</t>
-  </si>
-  <si>
-    <t>loss_function</t>
-  </si>
-  <si>
-    <t>optimizer1</t>
-  </si>
-  <si>
     <t>beta1</t>
   </si>
   <si>
-    <t>mini_batch</t>
-  </si>
-  <si>
-    <t>mini_batch_size</t>
-  </si>
-  <si>
     <t>Processing Time (s)</t>
   </si>
   <si>
-    <t>train_accuracy</t>
-  </si>
-  <si>
-    <t>test_accuracy</t>
-  </si>
-  <si>
-    <t>final_loss</t>
+    <t>Epoch</t>
+  </si>
+  <si>
+    <t>Learning Rate</t>
+  </si>
+  <si>
+    <t>hidden a</t>
+  </si>
+  <si>
+    <t>Output a</t>
+  </si>
+  <si>
+    <t>Dropout rate</t>
+  </si>
+  <si>
+    <t>Lambda L1</t>
+  </si>
+  <si>
+    <t>Lambda L2</t>
+  </si>
+  <si>
+    <t>Loss function</t>
+  </si>
+  <si>
+    <t>Optimizer</t>
+  </si>
+  <si>
+    <t>mini batch size</t>
+  </si>
+  <si>
+    <t>Train accuracy</t>
+  </si>
+  <si>
+    <t>Final Loss</t>
   </si>
   <si>
     <t>Test 1000 epochs, no dropout, no regularization, no mini-batch, sigmoid and softmax activations</t>
@@ -98,13 +92,31 @@
   </si>
   <si>
     <t>Test2 mini-batch</t>
+  </si>
+  <si>
+    <t>Test3 architecture 5 layers, lr=0.01, mini-batch, relu hidden, gradient-descent with mini batch</t>
+  </si>
+  <si>
+    <t>[33, 16, 8, 3]</t>
+  </si>
+  <si>
+    <t>Test4 architecture 1 layers, lr=0.01, mini-batch, relu hidden, gradient-descent without mini batch</t>
+  </si>
+  <si>
+    <t>Test accuracy</t>
+  </si>
+  <si>
+    <t>mini batch</t>
+  </si>
+  <si>
+    <t>0.9</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -117,6 +129,26 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -126,7 +158,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -149,15 +181,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -460,13 +510,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="16" max="16" width="12.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.77734375" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.77734375" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" customWidth="1"/>
+    <col min="8" max="8" width="17.44140625" customWidth="1"/>
+    <col min="11" max="11" width="12.21875" customWidth="1"/>
+    <col min="14" max="14" width="16.77734375" customWidth="1"/>
+    <col min="15" max="15" width="10.5546875" customWidth="1"/>
+    <col min="16" max="16" width="12.33203125" customWidth="1"/>
+    <col min="17" max="17" width="14.6640625" customWidth="1"/>
+    <col min="18" max="18" width="13.21875" customWidth="1"/>
+    <col min="19" max="19" width="13.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -474,66 +536,66 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="N1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="B2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
       <c r="C2">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="D2">
         <v>0.01</v>
@@ -542,10 +604,10 @@
         <v>42</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -557,39 +619,39 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2">
-        <v>0.9</v>
-      </c>
-      <c r="N2" t="b">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2">
         <v>1</v>
       </c>
       <c r="O2">
         <v>64</v>
       </c>
       <c r="P2">
+        <v>0.9375</v>
+      </c>
+      <c r="Q2">
+        <v>0.90439999999999998</v>
+      </c>
+      <c r="R2">
+        <v>3.611291624243109E-3</v>
+      </c>
+      <c r="S2">
         <v>0.20255231857299799</v>
       </c>
-      <c r="Q2">
-        <v>0.9375</v>
-      </c>
-      <c r="R2">
-        <v>0.90439999999999998</v>
-      </c>
-      <c r="S2">
-        <v>3.611291624243109E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C3">
         <v>3000</v>
@@ -601,10 +663,10 @@
         <v>42</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -616,34 +678,1206 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L3" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3">
-        <v>0.9</v>
-      </c>
-      <c r="N3" t="b">
+        <v>22</v>
+      </c>
+      <c r="M3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3">
         <v>1</v>
       </c>
       <c r="O3">
         <v>64</v>
       </c>
       <c r="P3">
+        <v>0.953125</v>
+      </c>
+      <c r="Q3">
+        <v>0.91444999999999999</v>
+      </c>
+      <c r="R3">
+        <v>2.8291984049081602E-3</v>
+      </c>
+      <c r="S3">
         <v>0.38754487037658691</v>
       </c>
-      <c r="Q3">
-        <v>0.953125</v>
-      </c>
-      <c r="R3">
-        <v>0.91444999999999999</v>
-      </c>
-      <c r="S3">
-        <v>2.8291984049081602E-3</v>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4">
+        <v>3000</v>
+      </c>
+      <c r="D4">
+        <v>0.01</v>
+      </c>
+      <c r="E4">
+        <v>42</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>64</v>
+      </c>
+      <c r="P4">
+        <v>0.94105000000000005</v>
+      </c>
+      <c r="Q4">
+        <v>0.94074999999999998</v>
+      </c>
+      <c r="R4">
+        <v>0.22124911518215251</v>
+      </c>
+      <c r="S4">
+        <v>229.76464104652399</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5">
+        <v>3000</v>
+      </c>
+      <c r="D5">
+        <v>0.01</v>
+      </c>
+      <c r="E5">
+        <v>42</v>
+      </c>
+      <c r="F5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>64</v>
+      </c>
+      <c r="P5">
+        <v>0.94105000000000005</v>
+      </c>
+      <c r="Q5">
+        <v>0.94074999999999998</v>
+      </c>
+      <c r="R5">
+        <v>0.22124911518215251</v>
+      </c>
+      <c r="S5">
+        <v>252.68180322647089</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6">
+        <v>3000</v>
+      </c>
+      <c r="D6">
+        <v>0.01</v>
+      </c>
+      <c r="E6">
+        <v>42</v>
+      </c>
+      <c r="F6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M6" t="s">
+        <v>29</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>64</v>
+      </c>
+      <c r="P6">
+        <v>0.96875</v>
+      </c>
+      <c r="Q6">
+        <v>0.92444999999999999</v>
+      </c>
+      <c r="R6">
+        <v>1.866644419287772E-3</v>
+      </c>
+      <c r="S6">
+        <v>2.4588239192962651</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7">
+        <v>3000</v>
+      </c>
+      <c r="D7">
+        <v>0.01</v>
+      </c>
+      <c r="E7">
+        <v>42</v>
+      </c>
+      <c r="F7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" t="s">
+        <v>22</v>
+      </c>
+      <c r="M7" t="s">
+        <v>29</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>32</v>
+      </c>
+      <c r="P7">
+        <v>0.96875</v>
+      </c>
+      <c r="Q7">
+        <v>0.93559999999999999</v>
+      </c>
+      <c r="R7">
+        <v>3.1096521212585549E-3</v>
+      </c>
+      <c r="S7">
+        <v>2.4103608131408691</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8">
+        <v>3000</v>
+      </c>
+      <c r="D8">
+        <v>0.01</v>
+      </c>
+      <c r="E8">
+        <v>42</v>
+      </c>
+      <c r="F8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M8" t="s">
+        <v>29</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>32</v>
+      </c>
+      <c r="P8">
+        <v>0.96875</v>
+      </c>
+      <c r="Q8">
+        <v>0.93569999999999998</v>
+      </c>
+      <c r="R8">
+        <v>3.1096521212585549E-3</v>
+      </c>
+      <c r="S8">
+        <v>0.62079954147338867</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9">
+        <v>3000</v>
+      </c>
+      <c r="D9">
+        <v>0.01</v>
+      </c>
+      <c r="E9">
+        <v>42</v>
+      </c>
+      <c r="F9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" t="s">
+        <v>22</v>
+      </c>
+      <c r="M9" t="s">
+        <v>29</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <v>32</v>
+      </c>
+      <c r="P9">
+        <v>0.96875</v>
+      </c>
+      <c r="Q9">
+        <v>0.93569999999999998</v>
+      </c>
+      <c r="R9">
+        <v>3.1096521212585549E-3</v>
+      </c>
+      <c r="S9">
+        <v>0.64668869972229004</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10">
+        <v>3000</v>
+      </c>
+      <c r="D10">
+        <v>0.01</v>
+      </c>
+      <c r="E10">
+        <v>42</v>
+      </c>
+      <c r="F10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M10" t="s">
+        <v>29</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>32</v>
+      </c>
+      <c r="P10">
+        <v>0.96875</v>
+      </c>
+      <c r="Q10">
+        <v>0.93569999999999998</v>
+      </c>
+      <c r="R10">
+        <v>3.1096521212585549E-3</v>
+      </c>
+      <c r="S10">
+        <v>0.6165168285369873</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11">
+        <v>3000</v>
+      </c>
+      <c r="D11">
+        <v>0.01</v>
+      </c>
+      <c r="E11">
+        <v>42</v>
+      </c>
+      <c r="F11" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M11" t="s">
+        <v>29</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>32</v>
+      </c>
+      <c r="P11">
+        <v>0.96875</v>
+      </c>
+      <c r="Q11">
+        <v>0.93569999999999998</v>
+      </c>
+      <c r="R11">
+        <v>9.9508867880273771E-2</v>
+      </c>
+      <c r="S11">
+        <v>0.64580154418945313</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12">
+        <v>3000</v>
+      </c>
+      <c r="D12">
+        <v>0.01</v>
+      </c>
+      <c r="E12">
+        <v>42</v>
+      </c>
+      <c r="F12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" t="s">
+        <v>22</v>
+      </c>
+      <c r="M12" t="s">
+        <v>29</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>32</v>
+      </c>
+      <c r="P12">
+        <v>0.93676250000000005</v>
+      </c>
+      <c r="Q12">
+        <v>0.93569999999999998</v>
+      </c>
+      <c r="R12">
+        <v>9.9508867880273771E-2</v>
+      </c>
+      <c r="S12">
+        <v>1.445015430450439</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13">
+        <v>3000</v>
+      </c>
+      <c r="D13">
+        <v>0.01</v>
+      </c>
+      <c r="E13">
+        <v>42</v>
+      </c>
+      <c r="F13" t="s">
+        <v>19</v>
+      </c>
+      <c r="G13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M13" t="s">
+        <v>29</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13">
+        <v>32</v>
+      </c>
+      <c r="P13">
+        <v>0.93676250000000005</v>
+      </c>
+      <c r="Q13">
+        <v>0.93569999999999998</v>
+      </c>
+      <c r="R13">
+        <v>9.9508867880273771E-2</v>
+      </c>
+      <c r="S13">
+        <v>1.5124998092651369</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14">
+        <v>100</v>
+      </c>
+      <c r="D14">
+        <v>0.01</v>
+      </c>
+      <c r="E14">
+        <v>42</v>
+      </c>
+      <c r="F14" t="s">
+        <v>19</v>
+      </c>
+      <c r="G14" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" t="s">
+        <v>22</v>
+      </c>
+      <c r="M14" t="s">
+        <v>29</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <v>32</v>
+      </c>
+      <c r="P14">
+        <v>0.93346249999999997</v>
+      </c>
+      <c r="Q14">
+        <v>0.93310000000000004</v>
+      </c>
+      <c r="R14">
+        <v>0.1294682666857615</v>
+      </c>
+      <c r="S14">
+        <v>0.24686217308044431</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15">
+        <v>10</v>
+      </c>
+      <c r="D15">
+        <v>0.01</v>
+      </c>
+      <c r="E15">
+        <v>42</v>
+      </c>
+      <c r="F15" t="s">
+        <v>19</v>
+      </c>
+      <c r="G15" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" t="s">
+        <v>22</v>
+      </c>
+      <c r="M15" t="s">
+        <v>29</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15">
+        <v>32</v>
+      </c>
+      <c r="P15">
+        <v>0.93346249999999997</v>
+      </c>
+      <c r="Q15">
+        <v>0.93310000000000004</v>
+      </c>
+      <c r="R15">
+        <v>0.1401326419568627</v>
+      </c>
+      <c r="S15">
+        <v>0.2371325492858887</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16">
+        <v>0.01</v>
+      </c>
+      <c r="E16">
+        <v>42</v>
+      </c>
+      <c r="F16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" t="s">
+        <v>22</v>
+      </c>
+      <c r="M16" t="s">
+        <v>29</v>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16">
+        <v>32</v>
+      </c>
+      <c r="P16">
+        <v>0.93346249999999997</v>
+      </c>
+      <c r="Q16">
+        <v>0.93310000000000004</v>
+      </c>
+      <c r="R16">
+        <v>0.1479507755714278</v>
+      </c>
+      <c r="S16">
+        <v>0.2371327877044678</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17">
+        <v>10</v>
+      </c>
+      <c r="D17">
+        <v>0.01</v>
+      </c>
+      <c r="E17">
+        <v>42</v>
+      </c>
+      <c r="F17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" t="s">
+        <v>22</v>
+      </c>
+      <c r="M17" t="s">
+        <v>29</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17">
+        <v>32</v>
+      </c>
+      <c r="P17">
+        <v>0.93346249999999997</v>
+      </c>
+      <c r="Q17">
+        <v>0.93310000000000004</v>
+      </c>
+      <c r="R17">
+        <v>0.1401326419568627</v>
+      </c>
+      <c r="S17">
+        <v>0.23761796951293951</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18">
+        <v>10</v>
+      </c>
+      <c r="D18">
+        <v>1E-3</v>
+      </c>
+      <c r="E18">
+        <v>42</v>
+      </c>
+      <c r="F18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G18" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18" t="s">
+        <v>22</v>
+      </c>
+      <c r="M18" t="s">
+        <v>29</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18">
+        <v>32</v>
+      </c>
+      <c r="P18">
+        <v>0.88575000000000004</v>
+      </c>
+      <c r="Q18">
+        <v>0.88344999999999996</v>
+      </c>
+      <c r="R18">
+        <v>0.40622512982999198</v>
+      </c>
+      <c r="S18">
+        <v>0.24925971031188959</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19">
+        <v>10</v>
+      </c>
+      <c r="D19">
+        <v>1E-3</v>
+      </c>
+      <c r="E19">
+        <v>42</v>
+      </c>
+      <c r="F19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G19" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" t="s">
+        <v>22</v>
+      </c>
+      <c r="M19" t="s">
+        <v>29</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19">
+        <v>32</v>
+      </c>
+      <c r="P19">
+        <v>0.88202499999999995</v>
+      </c>
+      <c r="Q19">
+        <v>0.88029999999999997</v>
+      </c>
+      <c r="R19">
+        <v>0.40622512982999198</v>
+      </c>
+      <c r="S19">
+        <v>0.53788924217224121</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20">
+        <v>10</v>
+      </c>
+      <c r="D20">
+        <v>1E-3</v>
+      </c>
+      <c r="E20">
+        <v>42</v>
+      </c>
+      <c r="F20" t="s">
+        <v>19</v>
+      </c>
+      <c r="G20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" t="s">
+        <v>22</v>
+      </c>
+      <c r="M20" t="s">
+        <v>29</v>
+      </c>
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20">
+        <v>32</v>
+      </c>
+      <c r="P20">
+        <v>0.88202499999999995</v>
+      </c>
+      <c r="Q20">
+        <v>0.88029999999999997</v>
+      </c>
+      <c r="R20">
+        <v>0.40622512982999198</v>
+      </c>
+      <c r="S20">
+        <v>0.55235934257507324</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21">
+        <v>10</v>
+      </c>
+      <c r="D21">
+        <v>1E-3</v>
+      </c>
+      <c r="E21">
+        <v>42</v>
+      </c>
+      <c r="F21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" t="s">
+        <v>20</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" t="s">
+        <v>22</v>
+      </c>
+      <c r="M21" t="s">
+        <v>29</v>
+      </c>
+      <c r="N21">
+        <v>1</v>
+      </c>
+      <c r="O21">
+        <v>32</v>
+      </c>
+      <c r="P21">
+        <v>0.88202499999999995</v>
+      </c>
+      <c r="Q21">
+        <v>0.88029999999999997</v>
+      </c>
+      <c r="R21">
+        <v>0.40622512982999198</v>
+      </c>
+      <c r="S21">
+        <v>0.61325573921203613</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22">
+        <v>10</v>
+      </c>
+      <c r="D22">
+        <v>1E-3</v>
+      </c>
+      <c r="E22">
+        <v>42</v>
+      </c>
+      <c r="F22" t="s">
+        <v>19</v>
+      </c>
+      <c r="G22" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" t="s">
+        <v>22</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N22">
+        <v>1</v>
+      </c>
+      <c r="O22">
+        <v>32</v>
+      </c>
+      <c r="P22">
+        <v>0.88202499999999995</v>
+      </c>
+      <c r="Q22">
+        <v>0.88029999999999997</v>
+      </c>
+      <c r="R22">
+        <v>0.40622512982999198</v>
+      </c>
+      <c r="S22">
+        <v>0.52090787887573242</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23">
+        <v>10</v>
+      </c>
+      <c r="D23">
+        <v>1E-3</v>
+      </c>
+      <c r="E23">
+        <v>42</v>
+      </c>
+      <c r="F23" t="s">
+        <v>19</v>
+      </c>
+      <c r="G23" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23" t="s">
+        <v>22</v>
+      </c>
+      <c r="M23" t="s">
+        <v>29</v>
+      </c>
+      <c r="N23">
+        <v>1</v>
+      </c>
+      <c r="O23">
+        <v>32</v>
+      </c>
+      <c r="P23">
+        <v>0.88202499999999995</v>
+      </c>
+      <c r="Q23">
+        <v>0.88029999999999997</v>
+      </c>
+      <c r="R23">
+        <v>0.40622512982999198</v>
+      </c>
+      <c r="S23">
+        <v>0.56305909156799316</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>